--- a/data/expenses.xlsx
+++ b/data/expenses.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -659,9 +659,35 @@
         <v>2026-03-02T13:50:07.865Z</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>2000</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Food</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="F11" t="str">
+        <v>UPI</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>2026-03-03T15:14:10.615Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
   </ignoredErrors>
 </worksheet>
 </file>